--- a/Ozora-2026-Import-Template.xlsx
+++ b/Ozora-2026-Import-Template.xlsx
@@ -559,7 +559,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ozora 2026 – Excel import template</t>
+          <t>Ozora 2026 – blank personal import</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Edit personal fields in the Import sheet, then choose this .xlsx file in the app. The file is processed locally in the browser and is not uploaded.</t>
+          <t>Blank workbook for your own ratings, comments, links and plan choices. It contains no pre-filled personal ratings, comments or links. Import is processed locally in the browser.</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The ID column is the safest match and must not be changed. Johannes-style workbooks without IDs are matched by artist name and, where available, stage/time.</t>
+          <t>Keep the ID column unchanged. It uniquely connects each row to the correct festival act.</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The TRUE values are based on the confident Ozora + Indian Spirit overlaps in Johannes' 'Overlap 2026' sheet.</t>
+          <t>TRUE marks the supplied Ozora + Indian Spirit 2026 overlap metadata; it is not personal rating data.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Schedule: supplied Ozora 2026 posters. Personal data: entered by the user. No external API is used.</t>
+          <t>Schedule: supplied Ozora 2026 posters. Personal fields are intentionally empty. No external API is used.</t>
         </is>
       </c>
     </row>
